--- a/data/invoices.xlsx
+++ b/data/invoices.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoices" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Invoices" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Invoices'!$A$1:$L$51</definedName>
@@ -577,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:Q51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="E2" s="4" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="E3" s="10" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="E4" s="13" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="E5" s="15" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="E8" s="13" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="E9" s="10" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="E11" s="15" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="E12" s="13" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="E13" s="15" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="E15" s="15" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="E17" s="8" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="E19" s="10" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="E21" s="10" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="E22" s="13" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         </is>
       </c>
       <c r="E23" s="15" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="E24" s="13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="E25" s="10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="E27" s="8" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="E29" s="15" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="E31" s="15" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         </is>
       </c>
       <c r="E32" s="13" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="E33" s="15" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="E35" s="15" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="E36" s="13" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="E37" s="10" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="E38" s="13" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         </is>
       </c>
       <c r="E39" s="10" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="E41" s="15" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="E43" s="8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         </is>
       </c>
       <c r="E45" s="8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="E46" s="13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="E47" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         </is>
       </c>
       <c r="E48" s="13" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="E49" s="15" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         </is>
       </c>
       <c r="E50" s="13" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         </is>
       </c>
       <c r="E51" s="15" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
@@ -3500,10 +3500,7 @@
           <t>Total Invoices</t>
         </is>
       </c>
-      <c r="B4" s="21">
-        <f>COUNTA(Invoices!A2:A51)</f>
-        <v/>
-      </c>
+      <c r="B4" s="21" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="21" t="inlineStr">
@@ -3511,10 +3508,7 @@
           <t>Total Outstanding (₹)</t>
         </is>
       </c>
-      <c r="B5" s="22">
-        <f>SUM(Invoices!C2:C51)</f>
-        <v/>
-      </c>
+      <c r="B5" s="22" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="21" t="inlineStr">
@@ -3522,10 +3516,7 @@
           <t>High Risk Invoices</t>
         </is>
       </c>
-      <c r="B6" s="21">
-        <f>COUNTIF(Invoices!J2:J51,"High")</f>
-        <v/>
-      </c>
+      <c r="B6" s="21" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="21" t="inlineStr">
@@ -3533,10 +3524,7 @@
           <t>Medium Risk Invoices</t>
         </is>
       </c>
-      <c r="B7" s="21">
-        <f>COUNTIF(Invoices!J2:J51,"Medium")</f>
-        <v/>
-      </c>
+      <c r="B7" s="21" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="21" t="inlineStr">
@@ -3544,10 +3532,7 @@
           <t>Low Risk Invoices</t>
         </is>
       </c>
-      <c r="B8" s="21">
-        <f>COUNTIF(Invoices!J2:J51,"Low")</f>
-        <v/>
-      </c>
+      <c r="B8" s="21" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="21" t="inlineStr">
@@ -3555,10 +3540,7 @@
           <t>Disputed Invoices</t>
         </is>
       </c>
-      <c r="B9" s="21">
-        <f>COUNTIF(Invoices!K2:K51,"Yes")</f>
-        <v/>
-      </c>
+      <c r="B9" s="21" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="21" t="inlineStr">
@@ -3566,10 +3548,7 @@
           <t>Missing Contact</t>
         </is>
       </c>
-      <c r="B10" s="21">
-        <f>COUNTIF(Invoices!G2:G51,"— MISSING —")</f>
-        <v/>
-      </c>
+      <c r="B10" s="21" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="21" t="inlineStr">
@@ -3577,10 +3556,7 @@
           <t>Avg Days Overdue</t>
         </is>
       </c>
-      <c r="B11" s="23">
-        <f>AVERAGE(Invoices!E2:E51)</f>
-        <v/>
-      </c>
+      <c r="B11" s="23" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="21" t="inlineStr">
@@ -3588,10 +3564,7 @@
           <t>Max Days Overdue</t>
         </is>
       </c>
-      <c r="B12" s="21">
-        <f>MAX(Invoices!E2:E51)</f>
-        <v/>
-      </c>
+      <c r="B12" s="21" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/invoices.xlsx
+++ b/data/invoices.xlsx
@@ -577,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q51"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="E3" s="10" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="E4" s="13" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="E5" s="15" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="E8" s="13" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="E11" s="15" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="E12" s="13" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="E13" s="15" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="E15" s="15" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="E17" s="8" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="E19" s="10" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="E21" s="10" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="E22" s="13" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         </is>
       </c>
       <c r="E23" s="15" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="E24" s="13" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="E25" s="10" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="E27" s="8" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="E29" s="15" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="E31" s="15" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         </is>
       </c>
       <c r="E32" s="13" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="E33" s="15" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="E35" s="15" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="E36" s="13" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="E37" s="10" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="E38" s="13" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         </is>
       </c>
       <c r="E39" s="10" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="E41" s="15" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="E43" s="8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         </is>
       </c>
       <c r="E45" s="8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="E46" s="13" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="E47" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         </is>
       </c>
       <c r="E48" s="13" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="E49" s="15" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         </is>
       </c>
       <c r="E50" s="13" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         </is>
       </c>
       <c r="E51" s="15" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>

--- a/data/invoices.xlsx
+++ b/data/invoices.xlsx
@@ -577,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:Q53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3453,6 +3453,156 @@
       <c r="L51" s="12" t="inlineStr">
         <is>
           <t>Schedule follow-up call</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>INV100</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Patel Industries</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>40445</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>38</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Kiran Patel</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>farazstudy112@gmail.com</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>55</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>send_urgent_followup</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>demo_engine</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:28:41.414138+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>INV101</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Khan &amp; Brothers</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>63176</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>45</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="n">
+        <v>61</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>resolve_contact_details</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>demo_engine</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:28:41.414138+00:00</t>
         </is>
       </c>
     </row>

--- a/data/invoices.xlsx
+++ b/data/invoices.xlsx
@@ -8,22 +8,16 @@
   </bookViews>
   <sheets>
     <sheet name="Invoices" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Invoices'!$A$1:$L$51</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="₹#,##0"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-  </numFmts>
-  <fonts count="10">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,58 +26,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="009C0006"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="009C5700"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="009C5700"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00276221"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <i val="1"/>
-      <color rgb="009C0006"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -92,36 +39,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F7FC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="002F4F8F"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -129,89 +51,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00CCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CCCCCC"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -579,22 +425,8 @@
   </sheetPr>
   <dimension ref="A1:Q53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Invoice ID</t>
@@ -652,2831 +484,3961 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Last Contact Date</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Last Contact Type</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Contact Count</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Next Action</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Last Updated By</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Last Updated At</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>INV001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Raj Traders</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" t="n">
         <v>87500</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>2026-02-17</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" t="n">
         <v>61</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>Rajesh Kumar</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>farazstudy112@gmail.com</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" t="n">
         <v>74</v>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L2" s="7" t="inlineStr">
-        <is>
-          <t>Escalate to legal team</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>schedule_call</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>INV002</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Raj Traders</t>
         </is>
       </c>
-      <c r="C3" s="9" t="n">
+      <c r="C3" t="n">
         <v>124000</v>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="E3" s="10" t="n">
+      <c r="E3" t="n">
         <v>71</v>
       </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>Rajesh Kumar</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>farazstudy112@gmail.com</t>
         </is>
       </c>
-      <c r="I3" s="8" t="n">
+      <c r="I3" t="n">
         <v>78</v>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K3" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L3" s="12" t="inlineStr">
-        <is>
-          <t>Escalate to legal team</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>schedule_call</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>INV003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Raj Traders</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" t="n">
         <v>45000</v>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="E4" s="13" t="n">
+      <c r="E4" t="n">
         <v>46</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>Rajesh Kumar</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>farazstudy112@gmail.com</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" t="n">
         <v>62</v>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t>Schedule follow-up call</t>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>schedule_call</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>INV004</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Raj Traders</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" t="n">
         <v>33000</v>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" t="n">
         <v>36</v>
       </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>Rajesh Kumar</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>farazstudy112@gmail.com</t>
         </is>
       </c>
-      <c r="I5" s="8" t="n">
+      <c r="I5" t="n">
         <v>55</v>
       </c>
-      <c r="J5" s="14" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K5" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
-          <t>Schedule follow-up call</t>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>schedule_call</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>INV005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Raj Traders</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" t="n">
         <v>19500</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" t="n">
         <v>26</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Rajesh Kumar</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>farazstudy112@gmail.com</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" t="n">
         <v>43</v>
       </c>
-      <c r="J6" s="14" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>Schedule follow-up call</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>schedule_call</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>INV006</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Raj Traders</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" t="n">
         <v>72000</v>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>2026-01-28</t>
         </is>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" t="n">
         <v>81</v>
       </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>Rajesh Kumar</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>farazstudy112@gmail.com</t>
         </is>
       </c>
-      <c r="I7" s="8" t="n">
+      <c r="I7" t="n">
         <v>82</v>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K7" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L7" s="12" t="inlineStr">
-        <is>
-          <t>Escalate to legal team</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>schedule_call</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>INV007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Raj Traders</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" t="n">
         <v>56800</v>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>2026-02-27</t>
         </is>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" t="n">
         <v>51</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>Rajesh Kumar</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>farazstudy112@gmail.com</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I8" t="n">
         <v>67</v>
       </c>
-      <c r="J8" s="14" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>Schedule follow-up call</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>schedule_call</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>INV008</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Raj Traders</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" t="n">
         <v>98000</v>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>2026-01-18</t>
         </is>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" t="n">
         <v>91</v>
       </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>Rajesh Kumar</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>farazstudy112@gmail.com</t>
         </is>
       </c>
-      <c r="I9" s="8" t="n">
+      <c r="I9" t="n">
         <v>88</v>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K9" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L9" s="12" t="inlineStr">
-        <is>
-          <t>Escalate to legal team</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>schedule_call</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>INV009</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Mehta Enterprises</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" t="n">
         <v>61000</v>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" t="n">
         <v>66</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>Priya Mehta</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>joybackpack@gmail.com</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="I10" t="n">
         <v>85</v>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L10" s="7" t="inlineStr">
-        <is>
-          <t>Escalate to legal team</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>send_final_notice</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>INV010</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Mehta Enterprises</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" t="n">
         <v>47000</v>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E11" t="n">
         <v>56</v>
       </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>Priya Mehta</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>joybackpack@gmail.com</t>
         </is>
       </c>
-      <c r="I11" s="8" t="n">
+      <c r="I11" t="n">
         <v>80</v>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L11" s="12" t="inlineStr">
-        <is>
-          <t>Escalate to legal team</t>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>send_final_notice</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>INV011</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Mehta Enterprises</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" t="n">
         <v>28500</v>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" t="n">
         <v>41</v>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>Priya Mehta</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>joybackpack@gmail.com</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="I12" t="n">
         <v>58</v>
       </c>
-      <c r="J12" s="14" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K12" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>Schedule follow-up call</t>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>send_final_notice</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>INV012</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Mehta Enterprises</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" t="n">
         <v>15000</v>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>
       </c>
-      <c r="E13" s="15" t="n">
+      <c r="E13" t="n">
         <v>31</v>
       </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>Priya Mehta</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>joybackpack@gmail.com</t>
         </is>
       </c>
-      <c r="I13" s="8" t="n">
+      <c r="I13" t="n">
         <v>48</v>
       </c>
-      <c r="J13" s="14" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K13" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L13" s="12" t="inlineStr">
-        <is>
-          <t>Schedule follow-up call</t>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>send_final_notice</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>INV013</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Mehta Enterprises</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" t="n">
         <v>82000</v>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>2026-01-23</t>
         </is>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" t="n">
         <v>86</v>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>Priya Mehta</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>joybackpack@gmail.com</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="I14" t="n">
         <v>91</v>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L14" s="7" t="inlineStr">
-        <is>
-          <t>Escalate to legal team</t>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>send_final_notice</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>INV014</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Mehta Enterprises</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" t="n">
         <v>37500</v>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="E15" s="15" t="n">
+      <c r="E15" t="n">
         <v>46</v>
       </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>Priya Mehta</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>joybackpack@gmail.com</t>
         </is>
       </c>
-      <c r="I15" s="8" t="n">
+      <c r="I15" t="n">
         <v>60</v>
       </c>
-      <c r="J15" s="14" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K15" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L15" s="12" t="inlineStr">
-        <is>
-          <t>Schedule follow-up call</t>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>send_final_notice</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>INV015</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Mehta Enterprises</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C16" t="n">
         <v>54000</v>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>2026-02-02</t>
         </is>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" t="n">
         <v>76</v>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>Priya Mehta</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>joybackpack@gmail.com</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="I16" t="n">
         <v>87</v>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>Escalate to legal team</t>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>send_final_notice</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>INV016</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Mehta Enterprises</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" t="n">
         <v>22000</v>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="E17" s="8" t="n">
+      <c r="E17" t="n">
         <v>26</v>
       </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>Priya Mehta</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>joybackpack@gmail.com</t>
         </is>
       </c>
-      <c r="I17" s="8" t="n">
+      <c r="I17" t="n">
         <v>44</v>
       </c>
-      <c r="J17" s="14" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K17" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L17" s="12" t="inlineStr">
-        <is>
-          <t>Schedule follow-up call</t>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>send_final_notice</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>INV017</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Sharma Logistics</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C18" t="n">
         <v>115000</v>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>2026-01-18</t>
         </is>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" t="n">
         <v>91</v>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>Vikram Sharma</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>soundrify@gmail.com</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="I18" t="n">
         <v>79</v>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K18" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L18" s="7" t="inlineStr">
-        <is>
-          <t>Escalate to legal team</t>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>send_urgent_followup</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>email_agent</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:38:34.823068+00:00</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>INV018</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Sharma Logistics</t>
         </is>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" t="n">
         <v>93000</v>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>2026-01-28</t>
         </is>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E19" t="n">
         <v>81</v>
       </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>Vikram Sharma</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>soundrify@gmail.com</t>
         </is>
       </c>
-      <c r="I19" s="8" t="n">
+      <c r="I19" t="n">
         <v>75</v>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K19" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L19" s="12" t="inlineStr">
-        <is>
-          <t>Escalate to legal team</t>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>send_urgent_followup</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>email_agent</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:38:35.009795+00:00</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>INV019</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Sharma Logistics</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C20" t="n">
         <v>67500</v>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" t="n">
         <v>71</v>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>Vikram Sharma</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>soundrify@gmail.com</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="I20" t="n">
         <v>71</v>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K20" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L20" s="7" t="inlineStr">
-        <is>
-          <t>Escalate to legal team</t>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>send_urgent_followup</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>email_agent</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:38:35.183577+00:00</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>INV020</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Sharma Logistics</t>
         </is>
       </c>
-      <c r="C21" s="9" t="n">
+      <c r="C21" t="n">
         <v>48000</v>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>2026-02-17</t>
         </is>
       </c>
-      <c r="E21" s="10" t="n">
+      <c r="E21" t="n">
         <v>61</v>
       </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>Vikram Sharma</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>soundrify@gmail.com</t>
         </is>
       </c>
-      <c r="I21" s="8" t="n">
+      <c r="I21" t="n">
         <v>68</v>
       </c>
-      <c r="J21" s="14" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K21" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L21" s="12" t="inlineStr">
-        <is>
-          <t>Schedule follow-up call</t>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>send_urgent_followup</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>email_agent</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:38:35.360497+00:00</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>INV021</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Sharma Logistics</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="C22" t="n">
         <v>31000</v>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>2026-02-27</t>
         </is>
       </c>
-      <c r="E22" s="13" t="n">
+      <c r="E22" t="n">
         <v>51</v>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>Vikram Sharma</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>soundrify@gmail.com</t>
         </is>
       </c>
-      <c r="I22" s="2" t="n">
+      <c r="I22" t="n">
         <v>63</v>
       </c>
-      <c r="J22" s="14" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K22" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L22" s="7" t="inlineStr">
-        <is>
-          <t>Schedule follow-up call</t>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>send_urgent_followup</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>email_agent</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:38:35.565142+00:00</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>INV022</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Sharma Logistics</t>
         </is>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" t="n">
         <v>77000</v>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="E23" s="15" t="n">
+      <c r="E23" t="n">
         <v>41</v>
       </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>Vikram Sharma</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>soundrify@gmail.com</t>
         </is>
       </c>
-      <c r="I23" s="8" t="n">
+      <c r="I23" t="n">
         <v>57</v>
       </c>
-      <c r="J23" s="14" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K23" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L23" s="12" t="inlineStr">
-        <is>
-          <t>Schedule follow-up call</t>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>send_urgent_followup</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>email_agent</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:38:35.720807+00:00</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>INV023</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Sharma Logistics</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="C24" t="n">
         <v>52000</v>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>
       </c>
-      <c r="E24" s="13" t="n">
+      <c r="E24" t="n">
         <v>31</v>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>Vikram Sharma</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>soundrify@gmail.com</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="I24" t="n">
         <v>51</v>
       </c>
-      <c r="J24" s="14" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K24" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L24" s="7" t="inlineStr">
-        <is>
-          <t>Schedule follow-up call</t>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>send_urgent_followup</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>email_agent</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:38:35.867078+00:00</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>INV024</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Sharma Logistics</t>
         </is>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C25" t="n">
         <v>140000</v>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>2026-01-08</t>
         </is>
       </c>
-      <c r="E25" s="10" t="n">
+      <c r="E25" t="n">
         <v>101</v>
       </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>Vikram Sharma</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>soundrify@gmail.com</t>
         </is>
       </c>
-      <c r="I25" s="8" t="n">
+      <c r="I25" t="n">
         <v>92</v>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K25" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L25" s="12" t="inlineStr">
-        <is>
-          <t>Escalate to legal team</t>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>send_urgent_followup</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>email_agent</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:38:36.023193+00:00</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>INV025</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Noor Supplies</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="C26" t="n">
         <v>8500</v>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" t="n">
         <v>21</v>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>Noorjahan Ansari</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>gp4453@myamu.ac.in</t>
         </is>
       </c>
-      <c r="I26" s="2" t="n">
+      <c r="I26" t="n">
         <v>18</v>
       </c>
-      <c r="J26" s="16" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K26" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L26" s="7" t="inlineStr">
-        <is>
-          <t>Send friendly reminder email</t>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>send_friendly_reminder</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>INV026</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Noor Supplies</t>
         </is>
       </c>
-      <c r="C27" s="9" t="n">
+      <c r="C27" t="n">
         <v>12000</v>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="E27" s="8" t="n">
+      <c r="E27" t="n">
         <v>26</v>
       </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>Noorjahan Ansari</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>gp4453@myamu.ac.in</t>
         </is>
       </c>
-      <c r="I27" s="8" t="n">
+      <c r="I27" t="n">
         <v>22</v>
       </c>
-      <c r="J27" s="16" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K27" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L27" s="12" t="inlineStr">
-        <is>
-          <t>Send friendly reminder email</t>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>send_friendly_reminder</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>INV027</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Noor Supplies</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="C28" t="n">
         <v>6800</v>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="E28" t="n">
         <v>16</v>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>Noorjahan Ansari</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>gp4453@myamu.ac.in</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n">
+      <c r="I28" t="n">
         <v>12</v>
       </c>
-      <c r="J28" s="16" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K28" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L28" s="7" t="inlineStr">
-        <is>
-          <t>Send friendly reminder email</t>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>send_friendly_reminder</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>INV028</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Noor Supplies</t>
         </is>
       </c>
-      <c r="C29" s="9" t="n">
+      <c r="C29" t="n">
         <v>9200</v>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>
       </c>
-      <c r="E29" s="15" t="n">
+      <c r="E29" t="n">
         <v>31</v>
       </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>Noorjahan Ansari</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>gp4453@myamu.ac.in</t>
         </is>
       </c>
-      <c r="I29" s="8" t="n">
+      <c r="I29" t="n">
         <v>28</v>
       </c>
-      <c r="J29" s="16" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K29" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L29" s="12" t="inlineStr">
-        <is>
-          <t>Send friendly reminder email</t>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>send_friendly_reminder</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>INV029</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Noor Supplies</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="C30" t="n">
         <v>5500</v>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="E30" t="n">
         <v>11</v>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>Noorjahan Ansari</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>gp4453@myamu.ac.in</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n">
+      <c r="I30" t="n">
         <v>8</v>
       </c>
-      <c r="J30" s="16" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K30" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L30" s="7" t="inlineStr">
-        <is>
-          <t>Send friendly reminder email</t>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>send_friendly_reminder</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>INV030</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Noor Supplies</t>
         </is>
       </c>
-      <c r="C31" s="9" t="n">
+      <c r="C31" t="n">
         <v>14500</v>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="E31" s="15" t="n">
+      <c r="E31" t="n">
         <v>36</v>
       </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>Noorjahan Ansari</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>gp4453@myamu.ac.in</t>
         </is>
       </c>
-      <c r="I31" s="8" t="n">
+      <c r="I31" t="n">
         <v>32</v>
       </c>
-      <c r="J31" s="16" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K31" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L31" s="12" t="inlineStr">
-        <is>
-          <t>Send friendly reminder email</t>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>send_friendly_reminder</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>INV031</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Noor Supplies</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="C32" t="n">
         <v>7100</v>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="E32" s="13" t="n">
+      <c r="E32" t="n">
         <v>41</v>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>Noorjahan Ansari</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>gp4453@myamu.ac.in</t>
         </is>
       </c>
-      <c r="I32" s="2" t="n">
+      <c r="I32" t="n">
         <v>36</v>
       </c>
-      <c r="J32" s="16" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K32" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L32" s="7" t="inlineStr">
-        <is>
-          <t>Send friendly reminder email</t>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>send_friendly_reminder</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>INV032</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Noor Supplies</t>
         </is>
       </c>
-      <c r="C33" s="9" t="n">
+      <c r="C33" t="n">
         <v>11300</v>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="E33" s="15" t="n">
+      <c r="E33" t="n">
         <v>46</v>
       </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t>Noorjahan Ansari</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>gp4453@myamu.ac.in</t>
         </is>
       </c>
-      <c r="I33" s="8" t="n">
+      <c r="I33" t="n">
         <v>39</v>
       </c>
-      <c r="J33" s="16" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K33" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L33" s="12" t="inlineStr">
-        <is>
-          <t>Send friendly reminder email</t>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>send_friendly_reminder</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>INV033</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Apex Solutions</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="C34" t="n">
         <v>76000</v>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>2026-02-17</t>
         </is>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="E34" t="n">
         <v>61</v>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G34" s="17" t="inlineStr">
-        <is>
-          <t>— MISSING —</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t>abdullasiddique027@gmail.com</t>
         </is>
       </c>
-      <c r="I34" s="2" t="n">
+      <c r="I34" t="n">
         <v>73</v>
       </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K34" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L34" s="7" t="inlineStr">
-        <is>
-          <t>Resolve contact details before proceeding</t>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>resolve_contact_details</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>INV034</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Apex Solutions</t>
         </is>
       </c>
-      <c r="C35" s="9" t="n">
+      <c r="C35" t="n">
         <v>54000</v>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="E35" s="15" t="n">
+      <c r="E35" t="n">
         <v>46</v>
       </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G35" s="18" t="inlineStr">
-        <is>
-          <t>— MISSING —</t>
-        </is>
-      </c>
-      <c r="H35" s="8" t="inlineStr">
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
         <is>
           <t>abdullasiddique027@gmail.com</t>
         </is>
       </c>
-      <c r="I35" s="8" t="n">
+      <c r="I35" t="n">
         <v>74</v>
       </c>
-      <c r="J35" s="5" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K35" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L35" s="12" t="inlineStr">
-        <is>
-          <t>Resolve contact details before proceeding</t>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>resolve_contact_details</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>INV035</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Apex Solutions</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="C36" t="n">
         <v>38000</v>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>2026-02-27</t>
         </is>
       </c>
-      <c r="E36" s="13" t="n">
+      <c r="E36" t="n">
         <v>51</v>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G36" s="17" t="inlineStr">
-        <is>
-          <t>— MISSING —</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t>abdullasiddique027@gmail.com</t>
         </is>
       </c>
-      <c r="I36" s="2" t="n">
+      <c r="I36" t="n">
         <v>72</v>
       </c>
-      <c r="J36" s="5" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K36" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L36" s="7" t="inlineStr">
-        <is>
-          <t>Resolve contact details before proceeding</t>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>resolve_contact_details</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>INV036</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Apex Solutions</t>
         </is>
       </c>
-      <c r="C37" s="9" t="n">
+      <c r="C37" t="n">
         <v>92000</v>
       </c>
-      <c r="D37" s="8" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="E37" s="10" t="n">
+      <c r="E37" t="n">
         <v>71</v>
       </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G37" s="18" t="inlineStr">
-        <is>
-          <t>— MISSING —</t>
-        </is>
-      </c>
-      <c r="H37" s="8" t="inlineStr">
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t>abdullasiddique027@gmail.com</t>
         </is>
       </c>
-      <c r="I37" s="8" t="n">
+      <c r="I37" t="n">
         <v>83</v>
       </c>
-      <c r="J37" s="5" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K37" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L37" s="12" t="inlineStr">
-        <is>
-          <t>Resolve contact details before proceeding</t>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>resolve_contact_details</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>INV037</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Apex Solutions</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="C38" t="n">
         <v>29000</v>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="E38" s="13" t="n">
+      <c r="E38" t="n">
         <v>36</v>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G38" s="17" t="inlineStr">
-        <is>
-          <t>— MISSING —</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t>abdullasiddique027@gmail.com</t>
         </is>
       </c>
-      <c r="I38" s="2" t="n">
+      <c r="I38" t="n">
         <v>72</v>
       </c>
-      <c r="J38" s="5" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K38" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L38" s="7" t="inlineStr">
-        <is>
-          <t>Resolve contact details before proceeding</t>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>resolve_contact_details</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>INV038</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Apex Solutions</t>
         </is>
       </c>
-      <c r="C39" s="9" t="n">
+      <c r="C39" t="n">
         <v>63000</v>
       </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>2026-01-28</t>
         </is>
       </c>
-      <c r="E39" s="10" t="n">
+      <c r="E39" t="n">
         <v>81</v>
       </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G39" s="18" t="inlineStr">
-        <is>
-          <t>— MISSING —</t>
-        </is>
-      </c>
-      <c r="H39" s="8" t="inlineStr">
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t>abdullasiddique027@gmail.com</t>
         </is>
       </c>
-      <c r="I39" s="8" t="n">
+      <c r="I39" t="n">
         <v>85</v>
       </c>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K39" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L39" s="12" t="inlineStr">
-        <is>
-          <t>Resolve contact details before proceeding</t>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>resolve_contact_details</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>INV039</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Apex Solutions</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="C40" t="n">
         <v>18500</v>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="E40" s="2" t="n">
+      <c r="E40" t="n">
         <v>26</v>
       </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G40" s="17" t="inlineStr">
-        <is>
-          <t>— MISSING —</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t>abdullasiddique027@gmail.com</t>
         </is>
       </c>
-      <c r="I40" s="2" t="n">
+      <c r="I40" t="n">
         <v>72</v>
       </c>
-      <c r="J40" s="5" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K40" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L40" s="7" t="inlineStr">
-        <is>
-          <t>Resolve contact details before proceeding</t>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>resolve_contact_details</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>INV040</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Apex Solutions</t>
         </is>
       </c>
-      <c r="C41" s="9" t="n">
+      <c r="C41" t="n">
         <v>44500</v>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="E41" s="15" t="n">
+      <c r="E41" t="n">
         <v>41</v>
       </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G41" s="18" t="inlineStr">
-        <is>
-          <t>— MISSING —</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="inlineStr">
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t>abdullasiddique027@gmail.com</t>
         </is>
       </c>
-      <c r="I41" s="8" t="n">
+      <c r="I41" t="n">
         <v>73</v>
       </c>
-      <c r="J41" s="5" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K41" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L41" s="12" t="inlineStr">
-        <is>
-          <t>Resolve contact details before proceeding</t>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>resolve_contact_details</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>INV041</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Apex Solutions</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="C42" t="n">
         <v>57000</v>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="E42" s="4" t="n">
+      <c r="E42" t="n">
         <v>66</v>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G42" s="17" t="inlineStr">
-        <is>
-          <t>— MISSING —</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
         <is>
           <t>abdullasiddique027@gmail.com</t>
         </is>
       </c>
-      <c r="I42" s="2" t="n">
+      <c r="I42" t="n">
         <v>79</v>
       </c>
-      <c r="J42" s="5" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K42" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L42" s="7" t="inlineStr">
-        <is>
-          <t>Resolve contact details before proceeding</t>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>resolve_contact_details</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>INV042</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Crescent Tech</t>
         </is>
       </c>
-      <c r="C43" s="9" t="n">
+      <c r="C43" t="n">
         <v>21000</v>
       </c>
-      <c r="D43" s="8" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="E43" s="8" t="n">
+      <c r="E43" t="n">
         <v>21</v>
       </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
         <is>
           <t>Aisha Siddiqui</t>
         </is>
       </c>
-      <c r="H43" s="8" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>farazstudy112@gmail.com</t>
         </is>
       </c>
-      <c r="I43" s="8" t="n">
+      <c r="I43" t="n">
         <v>20</v>
       </c>
-      <c r="J43" s="16" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K43" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L43" s="12" t="inlineStr">
-        <is>
-          <t>Send friendly reminder email</t>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>send_friendly_reminder</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>INV043</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Crescent Tech</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="C44" t="n">
         <v>34000</v>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="E44" s="2" t="n">
+      <c r="E44" t="n">
         <v>26</v>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
         <is>
           <t>Aisha Siddiqui</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>farazstudy112@gmail.com</t>
         </is>
       </c>
-      <c r="I44" s="2" t="n">
+      <c r="I44" t="n">
         <v>25</v>
       </c>
-      <c r="J44" s="16" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K44" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L44" s="7" t="inlineStr">
-        <is>
-          <t>Send friendly reminder email</t>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>send_friendly_reminder</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>INV044</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Crescent Tech</t>
         </is>
       </c>
-      <c r="C45" s="9" t="n">
+      <c r="C45" t="n">
         <v>15500</v>
       </c>
-      <c r="D45" s="8" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="E45" s="8" t="n">
+      <c r="E45" t="n">
         <v>16</v>
       </c>
-      <c r="F45" s="8" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G45" s="8" t="inlineStr">
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
         <is>
           <t>Aisha Siddiqui</t>
         </is>
       </c>
-      <c r="H45" s="8" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>farazstudy112@gmail.com</t>
         </is>
       </c>
-      <c r="I45" s="8" t="n">
+      <c r="I45" t="n">
         <v>15</v>
       </c>
-      <c r="J45" s="16" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K45" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L45" s="12" t="inlineStr">
-        <is>
-          <t>Send friendly reminder email</t>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>send_friendly_reminder</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>INV045</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Crescent Tech</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="C46" t="n">
         <v>47000</v>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>
       </c>
-      <c r="E46" s="13" t="n">
+      <c r="E46" t="n">
         <v>31</v>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
         <is>
           <t>Aisha Siddiqui</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>farazstudy112@gmail.com</t>
         </is>
       </c>
-      <c r="I46" s="2" t="n">
+      <c r="I46" t="n">
         <v>30</v>
       </c>
-      <c r="J46" s="16" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K46" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L46" s="7" t="inlineStr">
-        <is>
-          <t>Send friendly reminder email</t>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>send_friendly_reminder</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>INV046</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Crescent Tech</t>
         </is>
       </c>
-      <c r="C47" s="9" t="n">
+      <c r="C47" t="n">
         <v>28000</v>
       </c>
-      <c r="D47" s="8" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="E47" s="8" t="n">
+      <c r="E47" t="n">
         <v>11</v>
       </c>
-      <c r="F47" s="8" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G47" s="8" t="inlineStr">
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
         <is>
           <t>Aisha Siddiqui</t>
         </is>
       </c>
-      <c r="H47" s="8" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>farazstudy112@gmail.com</t>
         </is>
       </c>
-      <c r="I47" s="8" t="n">
+      <c r="I47" t="n">
         <v>10</v>
       </c>
-      <c r="J47" s="16" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K47" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L47" s="12" t="inlineStr">
-        <is>
-          <t>Send friendly reminder email</t>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>send_friendly_reminder</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>INV047</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Crescent Tech</t>
         </is>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="C48" t="n">
         <v>62000</v>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="E48" s="13" t="n">
+      <c r="E48" t="n">
         <v>36</v>
       </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
         <is>
           <t>Aisha Siddiqui</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>farazstudy112@gmail.com</t>
         </is>
       </c>
-      <c r="I48" s="2" t="n">
+      <c r="I48" t="n">
         <v>35</v>
       </c>
-      <c r="J48" s="16" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K48" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L48" s="7" t="inlineStr">
-        <is>
-          <t>Send friendly reminder email</t>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>send_friendly_reminder</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>INV048</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Crescent Tech</t>
         </is>
       </c>
-      <c r="C49" s="9" t="n">
+      <c r="C49" t="n">
         <v>53500</v>
       </c>
-      <c r="D49" s="8" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="E49" s="15" t="n">
+      <c r="E49" t="n">
         <v>41</v>
       </c>
-      <c r="F49" s="8" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G49" s="8" t="inlineStr">
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
         <is>
           <t>Aisha Siddiqui</t>
         </is>
       </c>
-      <c r="H49" s="8" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>farazstudy112@gmail.com</t>
         </is>
       </c>
-      <c r="I49" s="8" t="n">
+      <c r="I49" t="n">
         <v>38</v>
       </c>
-      <c r="J49" s="16" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K49" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L49" s="12" t="inlineStr">
-        <is>
-          <t>Send friendly reminder email</t>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>send_friendly_reminder</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>INV049</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Crescent Tech</t>
         </is>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="C50" t="n">
         <v>19000</v>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="E50" s="13" t="n">
+      <c r="E50" t="n">
         <v>46</v>
       </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
         <is>
           <t>Aisha Siddiqui</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>farazstudy112@gmail.com</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n">
+      <c r="I50" t="n">
         <v>40</v>
       </c>
-      <c r="J50" s="16" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K50" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L50" s="7" t="inlineStr">
-        <is>
-          <t>Send friendly reminder email</t>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>send_friendly_reminder</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>INV050</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Crescent Tech</t>
         </is>
       </c>
-      <c r="C51" s="9" t="n">
+      <c r="C51" t="n">
         <v>41000</v>
       </c>
-      <c r="D51" s="8" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>2026-02-27</t>
         </is>
       </c>
-      <c r="E51" s="15" t="n">
+      <c r="E51" t="n">
         <v>51</v>
       </c>
-      <c r="F51" s="8" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="G51" s="8" t="inlineStr">
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
         <is>
           <t>Aisha Siddiqui</t>
         </is>
       </c>
-      <c r="H51" s="8" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>farazstudy112@gmail.com</t>
         </is>
       </c>
-      <c r="I51" s="8" t="n">
+      <c r="I51" t="n">
         <v>41</v>
       </c>
-      <c r="J51" s="14" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K51" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L51" s="12" t="inlineStr">
-        <is>
-          <t>Schedule follow-up call</t>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>send_friendly_reminder</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>fix_script</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>2026-04-18T21:32:59.445347+00:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>INV100</t>
+          <t>INV102</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Patel Industries</t>
+          <t>Verma Exports</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>40445</v>
+        <v>216500</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3485,7 +4447,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Kiran Patel</t>
+          <t>Suresh Verma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3494,11 +4456,11 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3521,7 +4483,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>send_urgent_followup</t>
+          <t>schedule_call</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -3531,45 +4493,53 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-04-18T21:28:41.414138+00:00</t>
+          <t>2026-04-18T21:37:38.747156+00:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>INV101</t>
+          <t>INV103</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Khan &amp; Brothers</t>
+          <t>Sunrise Retail</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>63176</v>
+        <v>18692</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>overdue</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Ananya Sharma</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>farazstudy112@gmail.com</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3592,7 +4562,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>resolve_contact_details</t>
+          <t>send_friendly_reminder</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -3602,119 +4572,9 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-04-18T21:28:41.414138+00:00</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:L51"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="19" t="inlineStr">
-        <is>
-          <t>VoiceOS – Invoice Portfolio Summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="20" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="20" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="21" t="inlineStr">
-        <is>
-          <t>Total Invoices</t>
-        </is>
-      </c>
-      <c r="B4" s="21" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="21" t="inlineStr">
-        <is>
-          <t>Total Outstanding (₹)</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="21" t="inlineStr">
-        <is>
-          <t>High Risk Invoices</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="21" t="inlineStr">
-        <is>
-          <t>Medium Risk Invoices</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="21" t="inlineStr">
-        <is>
-          <t>Low Risk Invoices</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="21" t="inlineStr">
-        <is>
-          <t>Disputed Invoices</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="21" t="inlineStr">
-        <is>
-          <t>Missing Contact</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="21" t="inlineStr">
-        <is>
-          <t>Avg Days Overdue</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>Max Days Overdue</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="n"/>
+          <t>2026-04-18T21:37:38.749695+00:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
